--- a/artfynd/A 48992-2019 artfynd.xlsx
+++ b/artfynd/A 48992-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48992-2019 artfynd.xlsx
+++ b/artfynd/A 48992-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126178418</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103770</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jämtkrogen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>532677</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6945482</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48992-2019 artfynd.xlsx
+++ b/artfynd/A 48992-2019 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>126178418</v>
       </c>
       <c r="B4" t="n">
-        <v>103770</v>
+        <v>103772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48992-2019 artfynd.xlsx
+++ b/artfynd/A 48992-2019 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>126178418</v>
       </c>
       <c r="B4" t="n">
-        <v>103772</v>
+        <v>103774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48992-2019 artfynd.xlsx
+++ b/artfynd/A 48992-2019 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>126178418</v>
       </c>
       <c r="B4" t="n">
-        <v>103774</v>
+        <v>103778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48992-2019 artfynd.xlsx
+++ b/artfynd/A 48992-2019 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>126178418</v>
       </c>
       <c r="B4" t="n">
-        <v>103778</v>
+        <v>103791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48992-2019 artfynd.xlsx
+++ b/artfynd/A 48992-2019 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>126178418</v>
       </c>
       <c r="B4" t="n">
-        <v>103791</v>
+        <v>103794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48992-2019 artfynd.xlsx
+++ b/artfynd/A 48992-2019 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>126178418</v>
       </c>
       <c r="B4" t="n">
-        <v>103794</v>
+        <v>103803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
